--- a/saidas/saida_Palestra Rock In Rio (respostas).xlsx
+++ b/saidas/saida_Palestra Rock In Rio (respostas).xlsx
@@ -426,196 +426,196 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Certifico que Ana Letícia Isoppo Machado Dall Cortivo participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Ana Letícia Isoppo Machado Dall Cortivo participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Certifico que Anie dos Anjos Fatudo Magalhães participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Anie dos Anjos Fatudo Magalhães participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Certifico que Antônio Gide Santos de Lira participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Antônio Gide Santos de Lira participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Certifico que Arthur Vital dos Santos participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Arthur Vital dos Santos participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Certifico que Bernardo Garcia Amaral participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Bernardo Garcia Amaral participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Certifico que Bianca Nunes Mendonça do Carmo participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Bianca Nunes Mendonça do Carmo participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Certifico que Bruno Gomes do Nascimento Melo participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Bruno Gomes do Nascimento Melo participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Certifico que Cacau Grammatico participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Cacau Grammatico participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Certifico que Clara Biancardi participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Clara Biancardi participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Certifico que Clara Ferro Romero participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Clara Ferro Romero participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Certifico que Gabriela Dinis Dorle participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Gabriela Dinis Dorle participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Certifico que Guilherme Moreira participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Guilherme Moreira participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Certifico que Isadora de Mello Gomes participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Isadora de Mello Gomes participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Certifico que Jamilly Andrade de Medeiros participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Jamilly Andrade de Medeiros participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Certifico que João Marcelo Dias Vianna participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que João Marcelo Dias Vianna participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Certifico que José Guilherme de Vilhena Correia participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que José Guilherme de Vilhena Correia participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Certifico que Keidy Alves Pizzetti Amaro participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Keidy Alves Pizzetti Amaro participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Certifico que Luiza Pollo Santos participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Luiza Pollo Santos participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Certifico que Maria Antônia de Lima Soeiro participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Maria Antônia de Lima Soeiro participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Certifico que Maria Cecília Pinto de Macedo Araújo participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Maria Cecília Pinto de Macedo Araújo participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Certifico que Maria Clara Dantas Itapicurú participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Maria Clara Dantas Itapicurú participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Certifico que Mariana Fontanezi participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Mariana Fontanezi participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Certifico que Paola de Almeida Veiros participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Paola de Almeida Veiros participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Certifico que Pedro Artur Duran Oliveira participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Pedro Artur Duran Oliveira participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Certifico que Rafael Roldi de Araujo participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Rafael Roldi de Araujo participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Certifico que Rafaella Cruz Santos participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Rafaella Cruz Santos participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Certifico que Victor de Araujo Lima Ramos Barbalho Martins participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Victor de Araujo Lima Ramos Barbalho Martins participou da palestra.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Certifico que Vitória Oliveira Moro participou da palestra, com duração de 2h, ministrada por Rafael Sant’anna, promovida pela LACOM Jr, Empresa Júnior de Comunicação Digital da Fundação Getúlio Vargas, no dia 06 de maio de 2026.</t>
+          <t>Certifico que Vitória Oliveira Moro participou da palestra.</t>
         </is>
       </c>
     </row>
